--- a/data/trans_orig/IP19C05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C05-Habitat-trans_orig.xlsx
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>596</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104509</t>
+          <t>105003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>109466</t>
+          <t>109465</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107851</t>
+          <t>108740</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>215774</t>
+          <t>215304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221050</t>
+          <t>221048</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66086</t>
+          <t>66562</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74648</t>
+          <t>74270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143222</t>
+          <t>143192</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92142</t>
+          <t>90842</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84212</t>
+          <t>84392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89396</t>
+          <t>89400</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178862</t>
+          <t>178460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185162</t>
+          <t>185323</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,47 +2119,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8508</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7925</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>343090</t>
+          <t>343477</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>349664</t>
+          <t>349693</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,49 +2232,49 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>358199</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>353223</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>360432</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>358199</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>353806</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>360414</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1057</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>700022</t>
+          <t>700021</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>708970</t>
+          <t>709156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69389</t>
+          <t>69298</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69421</t>
+          <t>69123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74608</t>
+          <t>74613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140886</t>
+          <t>141154</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147754</t>
+          <t>147769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11067</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>106812</t>
+          <t>106709</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111983</t>
+          <t>111991</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106727</t>
+          <t>106363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113326</t>
+          <t>112760</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>216239</t>
+          <t>216559</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>224594</t>
+          <t>224641</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67055</t>
+          <t>67456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73160</t>
+          <t>73380</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146333</t>
+          <t>146705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153142</t>
+          <t>153129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>742</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86074</t>
+          <t>86372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92217</t>
+          <t>92235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>182595</t>
+          <t>182710</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>188529</t>
+          <t>188531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>338781</t>
+          <t>338143</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348967</t>
+          <t>348732</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>354820</t>
+          <t>354383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>363162</t>
+          <t>363154</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>696723</t>
+          <t>697157</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>710096</t>
+          <t>710277</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>836</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9884</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66962</t>
+          <t>66293</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67539</t>
+          <t>68330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74942</t>
+          <t>74961</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136753</t>
+          <t>136174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144952</t>
+          <t>144672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99598</t>
+          <t>99082</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105889</t>
+          <t>105879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>104887</t>
+          <t>105532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>207536</t>
+          <t>207204</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213935</t>
+          <t>213906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71335</t>
+          <t>70694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72738</t>
+          <t>73516</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146748</t>
+          <t>146604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151796</t>
+          <t>151795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101476</t>
+          <t>101378</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108286</t>
+          <t>108278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101669</t>
+          <t>101576</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>206351</t>
+          <t>206961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>214296</t>
+          <t>214273</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15038</t>
+          <t>16245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>23031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>347580</t>
+          <t>346373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>357703</t>
+          <t>357356</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>356614</t>
+          <t>356304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>365080</t>
+          <t>365149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>707587</t>
+          <t>707595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>720602</t>
+          <t>721589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C05-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>75673</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,74 +1065,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1882</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>596</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5058</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5068</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>4,6%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110946</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>107781</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>108179</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>105003</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>104993</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>109465</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>95,4%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,46%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110946</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>108740</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>340</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>215304</t>
+          <t>214986</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221048</t>
+          <t>221049</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,102 +1413,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3274</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2646</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3171</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3599</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4457</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3885</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>77227</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>74595</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68576</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>66562</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66037</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77227</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>74270</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,38%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>235</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143192</t>
+          <t>142620</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2204</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5857</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>873</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5147</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2204</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5651</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>87839</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>84186</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>89401</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>95116</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>90842</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>91595</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>87839</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>84392</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>89400</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>93,72%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>251</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178460</t>
+          <t>178867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185323</t>
+          <t>185331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2099,59 +2099,59 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>3387</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7453</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7349</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8508</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2207,67 +2207,67 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>358199</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>353796</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>360400</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>517</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>347543</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>343477</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>349693</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>343581</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>349675</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>358199</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>353223</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>360432</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>700021</t>
+          <t>700248</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>709156</t>
+          <t>709234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6182</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1494</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4620</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2215</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6119</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>73027</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>69060</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>74611</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>72424</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>69298</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>68713</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>73027</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>69123</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74613</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,06%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>196</t>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141154</t>
+          <t>140691</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147769</t>
+          <t>147762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8147</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1925</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5890</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5207</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4003</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1946</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8343</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110703</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>106559</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>112756</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>110674</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>106709</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>111991</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>107392</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>111992</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,38%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,46%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110703</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>106363</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>112760</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,73%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>329</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>216559</t>
+          <t>216838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>224641</t>
+          <t>224604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3403</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7041</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8205</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,57%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>71094</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67456</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>73380</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66292</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>73183</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,43%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,55%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146705</t>
+          <t>146914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153129</t>
+          <t>153138</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2464</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>742</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6605</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7062</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>90513</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>86372</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92235</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>85915</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>92229</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,35%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>92,4%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,2%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>248</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>182710</t>
+          <t>182122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>188531</t>
+          <t>188530</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11351</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9286</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5259</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15848</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5329</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15840</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6218</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2848</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11619</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>359784</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>354651</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>363202</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>491</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>344705</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>338143</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>348732</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>338151</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>348662</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>359784</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>354383</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>363154</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>697157</t>
+          <t>697090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>710277</t>
+          <t>709793</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7501</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1301</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4548</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4656</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3300</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>836</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7467</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72497</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>68296</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>74948</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,1%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>69540</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>66293</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>66185</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,16%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,43%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72497</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>68330</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74961</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>90,15%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,9%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>189</t>
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136174</t>
+          <t>137614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144672</t>
+          <t>145056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2745</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3773</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8101</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1793</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7637</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,52%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3060</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>107975</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>105847</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103410</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>99082</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>105879</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>99546</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>105390</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,48%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>107975</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>105532</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>207204</t>
+          <t>207511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213906</t>
+          <t>213920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5076</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1386</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4894</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3347</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76104</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>71787</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>74202</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>70694</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>70747</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76104</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>73516</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>227</t>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146604</t>
+          <t>146685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151795</t>
+          <t>151803</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2644</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7629</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6944</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,43%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1477</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5181</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>105280</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>101682</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>106363</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>101378</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>108278</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>102063</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>108276</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,63%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,33%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>105280</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>101576</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,62%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>284</t>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>206961</t>
+          <t>206241</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>214273</t>
+          <t>214303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2440</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11413</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9104</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5262</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16245</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5089</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15050</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6153</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2859</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11704</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23031</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>361855</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>356595</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>365568</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>514</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>353514</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>346373</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>357356</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>347568</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>357529</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>361855</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>356304</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>365149</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>707595</t>
+          <t>707825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>721589</t>
+          <t>720767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
